--- a/data/Flow01/chiffreAffaireTotal.xlsx
+++ b/data/Flow01/chiffreAffaireTotal.xlsx
@@ -74,7 +74,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>70568.59999999998</v>
+        <v>70568.60000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data/Flow01/chiffreAffaireTotal.xlsx
+++ b/data/Flow01/chiffreAffaireTotal.xlsx
@@ -74,7 +74,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>70928.6</v>
+        <v>70568.59999999992</v>
       </c>
     </row>
   </sheetData>

--- a/data/Flow01/chiffreAffaireTotal.xlsx
+++ b/data/Flow01/chiffreAffaireTotal.xlsx
@@ -74,7 +74,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>70568.59999999992</v>
+        <v>70568.60000000002</v>
       </c>
     </row>
   </sheetData>
